--- a/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
+++ b/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D2695-D222-455D-9E2A-EC74DDEB81D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE8EDCE-C5FE-4F0C-8B6B-3402C392C29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="114">
   <si>
     <t>James Craven</t>
   </si>
@@ -379,10 +379,13 @@
     <t>Conversion CF CS</t>
   </si>
   <si>
-    <t xml:space="preserve">Conversion CF CS </t>
-  </si>
-  <si>
-    <t>Scott Alford</t>
+    <t>Anthony Forshaw</t>
+  </si>
+  <si>
+    <t>Product Specialty</t>
+  </si>
+  <si>
+    <t>Location</t>
   </si>
 </sst>
 </file>
@@ -1107,63 +1110,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1458,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>70</v>
@@ -1543,7 +1553,7 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
         <v>70</v>
@@ -1638,7 +1648,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>70</v>
@@ -1733,7 +1743,7 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
@@ -1954,16 +1964,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>76</v>
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>85</v>
@@ -1980,16 +1990,16 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>85</v>
@@ -2006,16 +2016,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>106</v>
+        <v>68</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
@@ -2032,16 +2042,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" t="s">
-        <v>106</v>
+        <v>104</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -2080,34 +2090,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
+++ b/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE8EDCE-C5FE-4F0C-8B6B-3402C392C29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871941B3-9EC5-4B66-A417-C9ADB7922319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="1995" windowWidth="21600" windowHeight="11235" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -313,9 +313,6 @@
     <t>15</t>
   </si>
   <si>
-    <t>Aaron Ovedia</t>
-  </si>
-  <si>
     <t>Vice President, CF Operations</t>
   </si>
   <si>
@@ -386,6 +383,9 @@
   </si>
   <si>
     <t>Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Truett </t>
   </si>
 </sst>
 </file>
@@ -1126,32 +1126,32 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1201,13 +1201,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1218,13 +1218,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1235,47 +1235,47 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1447,7 +1447,7 @@
         <v>38</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -1458,7 +1458,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
         <v>70</v>
@@ -1542,7 +1542,7 @@
         <v>55</v>
       </c>
       <c r="AE2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -1553,7 +1553,7 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>70</v>
@@ -1637,7 +1637,7 @@
         <v>55</v>
       </c>
       <c r="AE3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -1732,7 +1732,7 @@
         <v>55</v>
       </c>
       <c r="AE4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -1743,7 +1743,7 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
@@ -1827,7 +1827,7 @@
         <v>55</v>
       </c>
       <c r="AE5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -1959,21 +1959,21 @@
         <v>86</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" t="s">
         <v>109</v>
       </c>
-      <c r="B2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" t="s">
-        <v>110</v>
-      </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>85</v>
@@ -1985,21 +1985,21 @@
         <v>87</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
         <v>109</v>
       </c>
-      <c r="B3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>85</v>
@@ -2011,7 +2011,7 @@
         <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2037,15 +2037,15 @@
         <v>87</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
@@ -2063,7 +2063,7 @@
         <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2090,18 +2090,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
         <v>108</v>
-      </c>
-      <c r="B3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2114,10 +2114,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
+++ b/TestData/LV_TMTT0049771_VerifyMACSVerballyEngagedAndConvertedIntoFullyEngagedEngagementAndRevenueAccrualIsAddedOnEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871941B3-9EC5-4B66-A417-C9ADB7922319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AE4D43-B26A-44FF-8B88-6976244D008C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="1995" windowWidth="21600" windowHeight="11235" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
